--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/UTAH_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/UTAH_2017.xlsx
@@ -499,7 +499,7 @@
         <v>11</v>
       </c>
       <c r="D8">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="9">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C117">
@@ -5071,7 +5071,7 @@
         <v>11</v>
       </c>
       <c r="D262">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="263">
@@ -5107,7 +5107,7 @@
         <v>11</v>
       </c>
       <c r="D264">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="265">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C274">
@@ -6475,7 +6475,7 @@
         <v>11</v>
       </c>
       <c r="D340">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="341">
@@ -6583,7 +6583,7 @@
         <v>11</v>
       </c>
       <c r="D346">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="347">
@@ -7249,7 +7249,7 @@
         <v>11</v>
       </c>
       <c r="D383">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="384">
@@ -8311,7 +8311,7 @@
         <v>11</v>
       </c>
       <c r="D442">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="443">
@@ -8383,7 +8383,7 @@
         <v>11</v>
       </c>
       <c r="D446">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="447">
@@ -8437,7 +8437,7 @@
         <v>11</v>
       </c>
       <c r="D449">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="450">
@@ -9355,7 +9355,7 @@
         <v>11</v>
       </c>
       <c r="D500">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="501">
@@ -10309,7 +10309,7 @@
         <v>11</v>
       </c>
       <c r="D553">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="554">
@@ -10363,7 +10363,7 @@
         <v>11</v>
       </c>
       <c r="D556">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="557">
@@ -10489,7 +10489,7 @@
         <v>11</v>
       </c>
       <c r="D563">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="564">
@@ -12451,7 +12451,7 @@
         <v>11</v>
       </c>
       <c r="D672">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="673">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C749">
@@ -15079,7 +15079,7 @@
         <v>11</v>
       </c>
       <c r="D818">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="819">
@@ -16267,7 +16267,7 @@
         <v>11</v>
       </c>
       <c r="D884">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="885">
@@ -16411,7 +16411,7 @@
         <v>11</v>
       </c>
       <c r="D892">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="893">
@@ -17905,7 +17905,7 @@
         <v>11</v>
       </c>
       <c r="D975">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="976">
@@ -18679,7 +18679,7 @@
         <v>11</v>
       </c>
       <c r="D1018">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="1019">
@@ -19111,7 +19111,7 @@
         <v>11</v>
       </c>
       <c r="D1042">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="1043">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1060">
@@ -19705,7 +19705,7 @@
         <v>11</v>
       </c>
       <c r="D1075">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="1076">
@@ -20533,7 +20533,7 @@
         <v>11</v>
       </c>
       <c r="D1121">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="1122">
@@ -20821,7 +20821,7 @@
         <v>11</v>
       </c>
       <c r="D1137">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="1138">
@@ -22441,7 +22441,7 @@
         <v>11</v>
       </c>
       <c r="D1227">
-        <v>0.0009576876197109525</v>
+        <v>0.0009576876197109524</v>
       </c>
     </row>
     <row r="1228">
